--- a/results/walkforward/walk_forward_QQQ.xlsx
+++ b/results/walkforward/walk_forward_QQQ.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="54" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="100" uniqueCount="48">
   <si>
     <t>Ticker</t>
   </si>
@@ -70,6 +70,93 @@
   </si>
   <si>
     <t>SharpeImprovement</t>
+  </si>
+  <si>
+    <t>BaselineReturnPct</t>
+  </si>
+  <si>
+    <t>ExposureReturnPct</t>
+  </si>
+  <si>
+    <t>BaselineMaxDrawdownPct</t>
+  </si>
+  <si>
+    <t>ExposureMaxDrawdownPct</t>
+  </si>
+  <si>
+    <t>BaselineSharpe</t>
+  </si>
+  <si>
+    <t>ExposureSharpe</t>
+  </si>
+  <si>
+    <t>BuyHoldBuyCount</t>
+  </si>
+  <si>
+    <t>BaselineBuyCount</t>
+  </si>
+  <si>
+    <t>ExposureBuyCount</t>
+  </si>
+  <si>
+    <t>BuyHoldSellCount</t>
+  </si>
+  <si>
+    <t>BaselineSellCount</t>
+  </si>
+  <si>
+    <t>ExposureSellCount</t>
+  </si>
+  <si>
+    <t>BuyHoldTradeCount</t>
+  </si>
+  <si>
+    <t>BaselineTradeCount</t>
+  </si>
+  <si>
+    <t>ExposureTradeCount</t>
+  </si>
+  <si>
+    <t>BuyHoldTimeInMarketPct</t>
+  </si>
+  <si>
+    <t>BaselineTimeInMarketPct</t>
+  </si>
+  <si>
+    <t>ExposureTimeInMarketPct</t>
+  </si>
+  <si>
+    <t>ExposureAveragePct</t>
+  </si>
+  <si>
+    <t>ExposureTurnoverTotal</t>
+  </si>
+  <si>
+    <t>BuyHoldExcessReturnPct</t>
+  </si>
+  <si>
+    <t>BaselineExcessReturnPct</t>
+  </si>
+  <si>
+    <t>ExposureExcessReturnPct</t>
+  </si>
+  <si>
+    <t>BuyHoldDrawdownImprovementPct</t>
+  </si>
+  <si>
+    <t>BaselineDrawdownImprovementPct</t>
+  </si>
+  <si>
+    <t>ExposureDrawdownImprovementPct</t>
+  </si>
+  <si>
+    <t>BuyHoldSharpeImprovement</t>
+  </si>
+  <si>
+    <t>BaselineSharpeImprovement</t>
+  </si>
+  <si>
+    <t>ExposureSharpeImprovement</t>
   </si>
 </sst>
 </file>
@@ -115,7 +202,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.83984375" customWidth="true"/>
@@ -123,19 +210,38 @@
     <col min="3" max="3" width="15.5234375" customWidth="true"/>
     <col min="4" max="4" width="15.5234375" customWidth="true"/>
     <col min="5" max="5" width="15.5234375" customWidth="true"/>
-    <col min="6" max="6" width="15.41796875" customWidth="true"/>
-    <col min="7" max="7" width="15.5234375" customWidth="true"/>
-    <col min="8" max="8" width="22.20703125" customWidth="true"/>
+    <col min="6" max="6" width="15.5234375" customWidth="true"/>
+    <col min="7" max="7" width="15.3671875" customWidth="true"/>
+    <col min="8" max="8" width="16.1015625" customWidth="true"/>
     <col min="9" max="9" width="22.3125" customWidth="true"/>
-    <col min="10" max="10" width="14.15625" customWidth="true"/>
-    <col min="11" max="11" width="13.20703125" customWidth="true"/>
-    <col min="12" max="12" width="8.7890625" customWidth="true"/>
-    <col min="13" max="13" width="8.5234375" customWidth="true"/>
-    <col min="14" max="14" width="10.3671875" customWidth="true"/>
-    <col min="15" max="15" width="14.734375" customWidth="true"/>
-    <col min="16" max="16" width="13.9453125" customWidth="true"/>
-    <col min="17" max="17" width="22.99609375" customWidth="true"/>
-    <col min="18" max="18" width="17.3671875" customWidth="true"/>
+    <col min="10" max="10" width="22.15625" customWidth="true"/>
+    <col min="11" max="11" width="22.89453125" customWidth="true"/>
+    <col min="12" max="12" width="13.20703125" customWidth="true"/>
+    <col min="13" max="13" width="14.15625" customWidth="true"/>
+    <col min="14" max="14" width="13.7890625" customWidth="true"/>
+    <col min="15" max="15" width="15.41796875" customWidth="true"/>
+    <col min="16" max="16" width="15.26171875" customWidth="true"/>
+    <col min="17" max="17" width="16" customWidth="true"/>
+    <col min="18" max="18" width="15.15625" customWidth="true"/>
+    <col min="19" max="19" width="15" customWidth="true"/>
+    <col min="20" max="20" width="15.734375" customWidth="true"/>
+    <col min="21" max="21" width="16.99609375" customWidth="true"/>
+    <col min="22" max="22" width="16.83984375" customWidth="true"/>
+    <col min="23" max="23" width="17.578125" customWidth="true"/>
+    <col min="24" max="24" width="21.3671875" customWidth="true"/>
+    <col min="25" max="25" width="21.20703125" customWidth="true"/>
+    <col min="26" max="26" width="21.9453125" customWidth="true"/>
+    <col min="27" max="27" width="17.20703125" customWidth="true"/>
+    <col min="28" max="28" width="19.5234375" customWidth="true"/>
+    <col min="29" max="29" width="20.578125" customWidth="true"/>
+    <col min="30" max="30" width="20.41796875" customWidth="true"/>
+    <col min="31" max="31" width="21.15625" customWidth="true"/>
+    <col min="32" max="32" width="29.62890625" customWidth="true"/>
+    <col min="33" max="33" width="29.47265625" customWidth="true"/>
+    <col min="34" max="34" width="30.20703125" customWidth="true"/>
+    <col min="35" max="35" width="23.99609375" customWidth="true"/>
+    <col min="36" max="36" width="23.83984375" customWidth="true"/>
+    <col min="37" max="37" width="24.578125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -155,43 +261,100 @@
         <v>5</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I1" s="0" t="s">
         <v>9</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K1" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="0" t="s">
-        <v>12</v>
-      </c>
       <c r="M1" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="S1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="U1" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="V1" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="W1" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="X1" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y1" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z1" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA1" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB1" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC1" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD1" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE1" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF1" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG1" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH1" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI1" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ1" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="AK1" s="0" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="2">
@@ -211,43 +374,100 @@
         <v>43465</v>
       </c>
       <c r="F2" s="0">
+        <v>-0.11405355793117078</v>
+      </c>
+      <c r="G2" s="0">
         <v>-4.4920741170864193</v>
       </c>
-      <c r="G2" s="0">
-        <v>-0.11405355793117078</v>
-      </c>
       <c r="H2" s="0">
-        <v>-22.799679280511675</v>
+        <v>-5.3872103465836263</v>
       </c>
       <c r="I2" s="0">
         <v>-22.799679280511707</v>
       </c>
       <c r="J2" s="0">
+        <v>-22.799679280511675</v>
+      </c>
+      <c r="K2" s="0">
+        <v>-17.983604983457958</v>
+      </c>
+      <c r="L2" s="0">
+        <v>0.10929987296124369</v>
+      </c>
+      <c r="M2" s="0">
         <v>-0.092838053094160655</v>
       </c>
-      <c r="K2" s="0">
-        <v>0.10929987296124369</v>
-      </c>
-      <c r="L2" s="0">
-        <v>1</v>
-      </c>
-      <c r="M2" s="0">
+      <c r="N2" s="0">
+        <v>-0.2817003034265031</v>
+      </c>
+      <c r="O2" s="0">
+        <v>1</v>
+      </c>
+      <c r="P2" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="0">
+        <v>1</v>
+      </c>
+      <c r="R2" s="0">
+        <v>0</v>
+      </c>
+      <c r="S2" s="0">
         <v>2</v>
       </c>
-      <c r="N2" s="0">
+      <c r="T2" s="0">
+        <v>2</v>
+      </c>
+      <c r="U2" s="0">
+        <v>0</v>
+      </c>
+      <c r="V2" s="0">
         <v>3</v>
       </c>
-      <c r="O2" s="0">
+      <c r="W2" s="0">
+        <v>45</v>
+      </c>
+      <c r="X2" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y2" s="0">
         <v>95.617529880478088</v>
       </c>
-      <c r="P2" s="0">
-        <v>-4.3780205591552486</v>
-      </c>
-      <c r="Q2" s="0">
-        <v>3.1974423109204508e-14</v>
-      </c>
-      <c r="R2" s="0">
+      <c r="Z2" s="0">
+        <v>95.617529880478088</v>
+      </c>
+      <c r="AA2" s="0">
+        <v>72.151394422310773</v>
+      </c>
+      <c r="AB2" s="0">
+        <v>9.3499999999999979</v>
+      </c>
+      <c r="AC2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="0">
+        <v>-4.3780205591552495</v>
+      </c>
+      <c r="AE2" s="0">
+        <v>-5.2731567886524555</v>
+      </c>
+      <c r="AF2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="0">
+        <v>3.3306690738754696e-14</v>
+      </c>
+      <c r="AH2" s="0">
+        <v>4.8160742970537518</v>
+      </c>
+      <c r="AI2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="0">
         <v>-0.20213792605540434</v>
+      </c>
+      <c r="AK2" s="0">
+        <v>-0.39100017638774676</v>
       </c>
     </row>
     <row r="3">
@@ -267,43 +487,100 @@
         <v>43830</v>
       </c>
       <c r="F3" s="0">
+        <v>38.958968156911354</v>
+      </c>
+      <c r="G3" s="0">
         <v>34.231854886127543</v>
       </c>
-      <c r="G3" s="0">
-        <v>38.958968156911354</v>
-      </c>
       <c r="H3" s="0">
-        <v>-10.977189830693002</v>
+        <v>25.080247347154373</v>
       </c>
       <c r="I3" s="0">
         <v>-10.977189830693035</v>
       </c>
       <c r="J3" s="0">
+        <v>-10.977189830693002</v>
+      </c>
+      <c r="K3" s="0">
+        <v>-8.0217714720302151</v>
+      </c>
+      <c r="L3" s="0">
+        <v>2.1156923103317657</v>
+      </c>
+      <c r="M3" s="0">
         <v>2.013074174394379</v>
       </c>
-      <c r="K3" s="0">
-        <v>2.1156923103317657</v>
-      </c>
-      <c r="L3" s="0">
-        <v>1</v>
-      </c>
-      <c r="M3" s="0">
-        <v>0</v>
-      </c>
       <c r="N3" s="0">
-        <v>1</v>
+        <v>2.0237723658766131</v>
       </c>
       <c r="O3" s="0">
+        <v>1</v>
+      </c>
+      <c r="P3" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="0">
+        <v>1</v>
+      </c>
+      <c r="R3" s="0">
+        <v>0</v>
+      </c>
+      <c r="S3" s="0">
+        <v>0</v>
+      </c>
+      <c r="T3" s="0">
+        <v>0</v>
+      </c>
+      <c r="U3" s="0">
+        <v>0</v>
+      </c>
+      <c r="V3" s="0">
+        <v>1</v>
+      </c>
+      <c r="W3" s="0">
+        <v>30</v>
+      </c>
+      <c r="X3" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y3" s="0">
         <v>98.412698412698404</v>
       </c>
-      <c r="P3" s="0">
-        <v>-4.7271132707838106</v>
-      </c>
-      <c r="Q3" s="0">
-        <v>3.3750779948604759e-14</v>
-      </c>
-      <c r="R3" s="0">
+      <c r="Z3" s="0">
+        <v>98.412698412698404</v>
+      </c>
+      <c r="AA3" s="0">
+        <v>78.472222222222229</v>
+      </c>
+      <c r="AB3" s="0">
+        <v>6.3499999999999996</v>
+      </c>
+      <c r="AC3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="0">
+        <v>-4.7271132707838115</v>
+      </c>
+      <c r="AE3" s="0">
+        <v>-13.878720809756985</v>
+      </c>
+      <c r="AF3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="0">
+        <v>3.3306690738754696e-14</v>
+      </c>
+      <c r="AH3" s="0">
+        <v>2.9554183586628202</v>
+      </c>
+      <c r="AI3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="0">
         <v>-0.10261813593738678</v>
+      </c>
+      <c r="AK3" s="0">
+        <v>-0.091919944455152613</v>
       </c>
     </row>
     <row r="4">
@@ -323,43 +600,100 @@
         <v>44196</v>
       </c>
       <c r="F4" s="0">
+        <v>48.646611788845327</v>
+      </c>
+      <c r="G4" s="0">
         <v>61.523048897890334</v>
       </c>
-      <c r="G4" s="0">
-        <v>48.646611788845327</v>
-      </c>
       <c r="H4" s="0">
-        <v>-14.690460020751194</v>
+        <v>46.869142634234251</v>
       </c>
       <c r="I4" s="0">
         <v>-28.555538592397166</v>
       </c>
       <c r="J4" s="0">
+        <v>-14.690460020751194</v>
+      </c>
+      <c r="K4" s="0">
+        <v>-12.072524537803741</v>
+      </c>
+      <c r="L4" s="0">
+        <v>1.2881262992720548</v>
+      </c>
+      <c r="M4" s="0">
         <v>2.0191604728746921</v>
       </c>
-      <c r="K4" s="0">
-        <v>1.2881262992720548</v>
-      </c>
-      <c r="L4" s="0">
+      <c r="N4" s="0">
+        <v>1.9784009080502873</v>
+      </c>
+      <c r="O4" s="0">
+        <v>1</v>
+      </c>
+      <c r="P4" s="0">
         <v>2</v>
       </c>
-      <c r="M4" s="0">
+      <c r="Q4" s="0">
         <v>2</v>
       </c>
-      <c r="N4" s="0">
+      <c r="R4" s="0">
+        <v>0</v>
+      </c>
+      <c r="S4" s="0">
+        <v>2</v>
+      </c>
+      <c r="T4" s="0">
+        <v>2</v>
+      </c>
+      <c r="U4" s="0">
+        <v>0</v>
+      </c>
+      <c r="V4" s="0">
         <v>4</v>
       </c>
-      <c r="O4" s="0">
+      <c r="W4" s="0">
+        <v>38</v>
+      </c>
+      <c r="X4" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y4" s="0">
         <v>88.537549407114625</v>
       </c>
-      <c r="P4" s="0">
-        <v>12.876437109045007</v>
-      </c>
-      <c r="Q4" s="0">
+      <c r="Z4" s="0">
+        <v>88.537549407114625</v>
+      </c>
+      <c r="AA4" s="0">
+        <v>72.529644268774746</v>
+      </c>
+      <c r="AB4" s="0">
+        <v>8.8999999999999986</v>
+      </c>
+      <c r="AC4" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="0">
+        <v>12.876437109045003</v>
+      </c>
+      <c r="AE4" s="0">
+        <v>-1.7774691546110777</v>
+      </c>
+      <c r="AF4" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="0">
         <v>13.865078571645972</v>
       </c>
-      <c r="R4" s="0">
+      <c r="AH4" s="0">
+        <v>16.483014054593426</v>
+      </c>
+      <c r="AI4" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="0">
         <v>0.73103417360263734</v>
+      </c>
+      <c r="AK4" s="0">
+        <v>0.69027460877823255</v>
       </c>
     </row>
     <row r="5">
@@ -379,43 +713,100 @@
         <v>44561</v>
       </c>
       <c r="F5" s="0">
+        <v>27.415609054036128</v>
+      </c>
+      <c r="G5" s="0">
         <v>25.793981127611442</v>
       </c>
-      <c r="G5" s="0">
-        <v>27.415609054036128</v>
-      </c>
       <c r="H5" s="0">
-        <v>-9.6136893959036023</v>
+        <v>20.102944661229948</v>
       </c>
       <c r="I5" s="0">
         <v>-10.851164422211756</v>
       </c>
       <c r="J5" s="0">
+        <v>-9.6136893959036023</v>
+      </c>
+      <c r="K5" s="0">
+        <v>-5.7471559636525722</v>
+      </c>
+      <c r="L5" s="0">
+        <v>1.4213058130654794</v>
+      </c>
+      <c r="M5" s="0">
         <v>1.4304937806722802</v>
       </c>
-      <c r="K5" s="0">
-        <v>1.4213058130654794</v>
-      </c>
-      <c r="L5" s="0">
-        <v>1</v>
-      </c>
-      <c r="M5" s="0">
-        <v>1</v>
-      </c>
       <c r="N5" s="0">
+        <v>1.5243718972438316</v>
+      </c>
+      <c r="O5" s="0">
+        <v>1</v>
+      </c>
+      <c r="P5" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="0">
+        <v>1</v>
+      </c>
+      <c r="R5" s="0">
+        <v>0</v>
+      </c>
+      <c r="S5" s="0">
+        <v>1</v>
+      </c>
+      <c r="T5" s="0">
+        <v>1</v>
+      </c>
+      <c r="U5" s="0">
+        <v>0</v>
+      </c>
+      <c r="V5" s="0">
         <v>2</v>
       </c>
-      <c r="O5" s="0">
+      <c r="W5" s="0">
+        <v>41</v>
+      </c>
+      <c r="X5" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y5" s="0">
         <v>96.428571428571431</v>
       </c>
-      <c r="P5" s="0">
-        <v>-1.6216279264246864</v>
-      </c>
-      <c r="Q5" s="0">
-        <v>1.2374750263081538</v>
-      </c>
-      <c r="R5" s="0">
+      <c r="Z5" s="0">
+        <v>96.428571428571431</v>
+      </c>
+      <c r="AA5" s="0">
+        <v>75.813492063492092</v>
+      </c>
+      <c r="AB5" s="0">
+        <v>8.5999999999999979</v>
+      </c>
+      <c r="AC5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="0">
+        <v>-1.6216279264246847</v>
+      </c>
+      <c r="AE5" s="0">
+        <v>-7.3126643928061785</v>
+      </c>
+      <c r="AF5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="0">
+        <v>1.2374750263081546</v>
+      </c>
+      <c r="AH5" s="0">
+        <v>5.1040084585591838</v>
+      </c>
+      <c r="AI5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="0">
         <v>0.0091879676068007399</v>
+      </c>
+      <c r="AK5" s="0">
+        <v>0.10306608417835217</v>
       </c>
     </row>
     <row r="6">
@@ -435,43 +826,100 @@
         <v>44926</v>
       </c>
       <c r="F6" s="0">
+        <v>-32.57679027558499</v>
+      </c>
+      <c r="G6" s="0">
         <v>-25.132235220401721</v>
       </c>
-      <c r="G6" s="0">
-        <v>-32.57679027558499</v>
-      </c>
       <c r="H6" s="0">
-        <v>-28.939803276333176</v>
+        <v>-21.068242072273225</v>
       </c>
       <c r="I6" s="0">
         <v>-34.82849805487043</v>
       </c>
       <c r="J6" s="0">
+        <v>-28.939803276333176</v>
+      </c>
+      <c r="K6" s="0">
+        <v>-22.614296836887803</v>
+      </c>
+      <c r="L6" s="0">
+        <v>-1.0697619943744303</v>
+      </c>
+      <c r="M6" s="0">
         <v>-1.0451428517986023</v>
       </c>
-      <c r="K6" s="0">
-        <v>-1.0697619943744303</v>
-      </c>
-      <c r="L6" s="0">
+      <c r="N6" s="0">
+        <v>-1.2361883195974954</v>
+      </c>
+      <c r="O6" s="0">
+        <v>1</v>
+      </c>
+      <c r="P6" s="0">
         <v>4</v>
       </c>
-      <c r="M6" s="0">
+      <c r="Q6" s="0">
+        <v>4</v>
+      </c>
+      <c r="R6" s="0">
+        <v>0</v>
+      </c>
+      <c r="S6" s="0">
         <v>5</v>
       </c>
-      <c r="N6" s="0">
+      <c r="T6" s="0">
+        <v>5</v>
+      </c>
+      <c r="U6" s="0">
+        <v>0</v>
+      </c>
+      <c r="V6" s="0">
         <v>9</v>
       </c>
-      <c r="O6" s="0">
+      <c r="W6" s="0">
+        <v>49</v>
+      </c>
+      <c r="X6" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y6" s="0">
         <v>66.533864541832671</v>
       </c>
-      <c r="P6" s="0">
-        <v>7.4445550551832689</v>
-      </c>
-      <c r="Q6" s="0">
-        <v>5.8886947785372534</v>
-      </c>
-      <c r="R6" s="0">
+      <c r="Z6" s="0">
+        <v>66.533864541832671</v>
+      </c>
+      <c r="AA6" s="0">
+        <v>49.302788844621517</v>
+      </c>
+      <c r="AB6" s="0">
+        <v>12.750000000000002</v>
+      </c>
+      <c r="AC6" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="0">
+        <v>7.4445550551832662</v>
+      </c>
+      <c r="AE6" s="0">
+        <v>11.508548203311763</v>
+      </c>
+      <c r="AF6" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="0">
+        <v>5.8886947785372517</v>
+      </c>
+      <c r="AH6" s="0">
+        <v>12.214201217982623</v>
+      </c>
+      <c r="AI6" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="0">
         <v>0.024619142575827979</v>
+      </c>
+      <c r="AK6" s="0">
+        <v>-0.16642632522306511</v>
       </c>
     </row>
     <row r="7">
@@ -491,43 +939,100 @@
         <v>45291</v>
       </c>
       <c r="F7" s="0">
+        <v>54.774460567246884</v>
+      </c>
+      <c r="G7" s="0">
         <v>47.54353765718524</v>
       </c>
-      <c r="G7" s="0">
-        <v>54.774460567246884</v>
-      </c>
       <c r="H7" s="0">
-        <v>-10.779794273733811</v>
+        <v>36.452022486729696</v>
       </c>
       <c r="I7" s="0">
         <v>-10.77979427373389</v>
       </c>
       <c r="J7" s="0">
+        <v>-10.779794273733811</v>
+      </c>
+      <c r="K7" s="0">
+        <v>-8.0085817584338308</v>
+      </c>
+      <c r="L7" s="0">
+        <v>2.5553125137272699</v>
+      </c>
+      <c r="M7" s="0">
         <v>2.3315810896769724</v>
       </c>
-      <c r="K7" s="0">
-        <v>2.5553125137272699</v>
-      </c>
-      <c r="L7" s="0">
-        <v>1</v>
-      </c>
-      <c r="M7" s="0">
-        <v>0</v>
-      </c>
       <c r="N7" s="0">
-        <v>1</v>
+        <v>2.2675660552610277</v>
       </c>
       <c r="O7" s="0">
+        <v>1</v>
+      </c>
+      <c r="P7" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="0">
+        <v>1</v>
+      </c>
+      <c r="R7" s="0">
+        <v>0</v>
+      </c>
+      <c r="S7" s="0">
+        <v>0</v>
+      </c>
+      <c r="T7" s="0">
+        <v>0</v>
+      </c>
+      <c r="U7" s="0">
+        <v>0</v>
+      </c>
+      <c r="V7" s="0">
+        <v>1</v>
+      </c>
+      <c r="W7" s="0">
+        <v>44</v>
+      </c>
+      <c r="X7" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y7" s="0">
         <v>97.200000000000003</v>
       </c>
-      <c r="P7" s="0">
+      <c r="Z7" s="0">
+        <v>97.200000000000003</v>
+      </c>
+      <c r="AA7" s="0">
+        <v>77.40000000000002</v>
+      </c>
+      <c r="AB7" s="0">
+        <v>8.3499999999999996</v>
+      </c>
+      <c r="AC7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="0">
         <v>-7.2309229100616434</v>
       </c>
-      <c r="Q7" s="0">
-        <v>7.815970093361102e-14</v>
-      </c>
-      <c r="R7" s="0">
+      <c r="AE7" s="0">
+        <v>-18.322438080517188</v>
+      </c>
+      <c r="AF7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="0">
+        <v>7.7715611723760958e-14</v>
+      </c>
+      <c r="AH7" s="0">
+        <v>2.7712125153000589</v>
+      </c>
+      <c r="AI7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="0">
         <v>-0.22373142405029744</v>
+      </c>
+      <c r="AK7" s="0">
+        <v>-0.28774645846624214</v>
       </c>
     </row>
     <row r="8">
@@ -547,43 +1052,100 @@
         <v>45657</v>
       </c>
       <c r="F8" s="0">
+        <v>25.578174393289043</v>
+      </c>
+      <c r="G8" s="0">
         <v>19.143199015732982</v>
       </c>
-      <c r="G8" s="0">
-        <v>25.578174393289043</v>
-      </c>
       <c r="H8" s="0">
-        <v>-15.361647384867293</v>
+        <v>11.823825591436755</v>
       </c>
       <c r="I8" s="0">
         <v>-13.557819053325337</v>
       </c>
       <c r="J8" s="0">
+        <v>-15.361647384867293</v>
+      </c>
+      <c r="K8" s="0">
+        <v>-10.750324194239314</v>
+      </c>
+      <c r="L8" s="0">
+        <v>1.3552713153828093</v>
+      </c>
+      <c r="M8" s="0">
         <v>1.1482499157946466</v>
       </c>
-      <c r="K8" s="0">
-        <v>1.3552713153828093</v>
-      </c>
-      <c r="L8" s="0">
-        <v>1</v>
-      </c>
-      <c r="M8" s="0">
-        <v>1</v>
-      </c>
       <c r="N8" s="0">
+        <v>0.9634445426631002</v>
+      </c>
+      <c r="O8" s="0">
+        <v>1</v>
+      </c>
+      <c r="P8" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="0">
+        <v>1</v>
+      </c>
+      <c r="R8" s="0">
+        <v>0</v>
+      </c>
+      <c r="S8" s="0">
+        <v>1</v>
+      </c>
+      <c r="T8" s="0">
+        <v>1</v>
+      </c>
+      <c r="U8" s="0">
+        <v>0</v>
+      </c>
+      <c r="V8" s="0">
         <v>2</v>
       </c>
-      <c r="O8" s="0">
+      <c r="W8" s="0">
+        <v>45</v>
+      </c>
+      <c r="X8" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y8" s="0">
         <v>94.444444444444443</v>
       </c>
-      <c r="P8" s="0">
-        <v>-6.4349753775560607</v>
-      </c>
-      <c r="Q8" s="0">
-        <v>-1.8038283315419559</v>
-      </c>
-      <c r="R8" s="0">
+      <c r="Z8" s="0">
+        <v>94.444444444444443</v>
+      </c>
+      <c r="AA8" s="0">
+        <v>73.888888888888886</v>
+      </c>
+      <c r="AB8" s="0">
+        <v>9.0999999999999996</v>
+      </c>
+      <c r="AC8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="0">
+        <v>-6.4349753775560625</v>
+      </c>
+      <c r="AE8" s="0">
+        <v>-13.75434880185229</v>
+      </c>
+      <c r="AF8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="0">
+        <v>-1.8038283315419568</v>
+      </c>
+      <c r="AH8" s="0">
+        <v>2.8074948590860238</v>
+      </c>
+      <c r="AI8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="0">
         <v>-0.20702139958816268</v>
+      </c>
+      <c r="AK8" s="0">
+        <v>-0.39182677271970912</v>
       </c>
     </row>
     <row r="9">
@@ -603,43 +1165,100 @@
         <v>46022</v>
       </c>
       <c r="F9" s="0">
+        <v>20.342273477919193</v>
+      </c>
+      <c r="G9" s="0">
         <v>14.880317265055321</v>
       </c>
-      <c r="G9" s="0">
-        <v>20.342273477919193</v>
-      </c>
       <c r="H9" s="0">
-        <v>-26.273655940866458</v>
+        <v>9.2212972248572953</v>
       </c>
       <c r="I9" s="0">
         <v>-22.768355184633116</v>
       </c>
       <c r="J9" s="0">
+        <v>-26.273655940866458</v>
+      </c>
+      <c r="K9" s="0">
+        <v>-18.983435327603026</v>
+      </c>
+      <c r="L9" s="0">
+        <v>0.90766215046721255</v>
+      </c>
+      <c r="M9" s="0">
         <v>0.71767420956184058</v>
       </c>
-      <c r="K9" s="0">
-        <v>0.90766215046721255</v>
-      </c>
-      <c r="L9" s="0">
-        <v>1</v>
-      </c>
-      <c r="M9" s="0">
-        <v>1</v>
-      </c>
       <c r="N9" s="0">
+        <v>0.64191734380263643</v>
+      </c>
+      <c r="O9" s="0">
+        <v>1</v>
+      </c>
+      <c r="P9" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="0">
+        <v>1</v>
+      </c>
+      <c r="R9" s="0">
+        <v>0</v>
+      </c>
+      <c r="S9" s="0">
+        <v>1</v>
+      </c>
+      <c r="T9" s="0">
+        <v>1</v>
+      </c>
+      <c r="U9" s="0">
+        <v>0</v>
+      </c>
+      <c r="V9" s="0">
         <v>2</v>
       </c>
-      <c r="O9" s="0">
+      <c r="W9" s="0">
+        <v>38</v>
+      </c>
+      <c r="X9" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y9" s="0">
         <v>95.599999999999994</v>
       </c>
-      <c r="P9" s="0">
-        <v>-5.4619562128638712</v>
-      </c>
-      <c r="Q9" s="0">
+      <c r="Z9" s="0">
+        <v>95.599999999999994</v>
+      </c>
+      <c r="AA9" s="0">
+        <v>75.100000000000009</v>
+      </c>
+      <c r="AB9" s="0">
+        <v>7.8999999999999986</v>
+      </c>
+      <c r="AC9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="0">
+        <v>-5.4619562128638721</v>
+      </c>
+      <c r="AE9" s="0">
+        <v>-11.120976253061897</v>
+      </c>
+      <c r="AF9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="0">
         <v>-3.5053007562333427</v>
       </c>
-      <c r="R9" s="0">
+      <c r="AH9" s="0">
+        <v>3.784919857030089</v>
+      </c>
+      <c r="AI9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="0">
         <v>-0.18998794090537197</v>
+      </c>
+      <c r="AK9" s="0">
+        <v>-0.26574480666457612</v>
       </c>
     </row>
     <row r="10">
@@ -665,37 +1284,94 @@
         <v>20.185248490175912</v>
       </c>
       <c r="H10" s="0">
-        <v>-11.83474937620419</v>
+        <v>16.393629153729684</v>
       </c>
       <c r="I10" s="0">
         <v>-11.83474937620419</v>
       </c>
       <c r="J10" s="0">
+        <v>-11.83474937620419</v>
+      </c>
+      <c r="K10" s="0">
+        <v>-8.5873381591971771</v>
+      </c>
+      <c r="L10" s="0">
         <v>2.6103479861647885</v>
       </c>
-      <c r="K10" s="0">
+      <c r="M10" s="0">
         <v>2.6103479861647885</v>
       </c>
-      <c r="L10" s="0">
-        <v>0</v>
-      </c>
-      <c r="M10" s="0">
-        <v>0</v>
-      </c>
       <c r="N10" s="0">
-        <v>0</v>
+        <v>2.7306819884636302</v>
       </c>
       <c r="O10" s="0">
+        <v>1</v>
+      </c>
+      <c r="P10" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="0">
+        <v>0</v>
+      </c>
+      <c r="R10" s="0">
+        <v>0</v>
+      </c>
+      <c r="S10" s="0">
+        <v>0</v>
+      </c>
+      <c r="T10" s="0">
+        <v>0</v>
+      </c>
+      <c r="U10" s="0">
+        <v>0</v>
+      </c>
+      <c r="V10" s="0">
+        <v>0</v>
+      </c>
+      <c r="W10" s="0">
+        <v>15</v>
+      </c>
+      <c r="X10" s="0">
         <v>100</v>
       </c>
-      <c r="P10" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="0">
-        <v>0</v>
-      </c>
-      <c r="R10" s="0">
-        <v>0</v>
+      <c r="Y10" s="0">
+        <v>100</v>
+      </c>
+      <c r="Z10" s="0">
+        <v>100</v>
+      </c>
+      <c r="AA10" s="0">
+        <v>79.215686274509807</v>
+      </c>
+      <c r="AB10" s="0">
+        <v>2.6999999999999997</v>
+      </c>
+      <c r="AC10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="0">
+        <v>-3.7916193364462281</v>
+      </c>
+      <c r="AF10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="0">
+        <v>3.2474112170070124</v>
+      </c>
+      <c r="AI10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="0">
+        <v>0.12033400229884172</v>
       </c>
     </row>
   </sheetData>

--- a/results/walkforward/walk_forward_QQQ.xlsx
+++ b/results/walkforward/walk_forward_QQQ.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="100" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="192" uniqueCount="48">
   <si>
     <t>Ticker</t>
   </si>
@@ -380,7 +380,7 @@
         <v>-4.4920741170864193</v>
       </c>
       <c r="H2" s="0">
-        <v>-5.3872103465836263</v>
+        <v>-7.5770487315697688</v>
       </c>
       <c r="I2" s="0">
         <v>-22.799679280511707</v>
@@ -389,7 +389,7 @@
         <v>-22.799679280511675</v>
       </c>
       <c r="K2" s="0">
-        <v>-17.983604983457958</v>
+        <v>-23.024255244266168</v>
       </c>
       <c r="L2" s="0">
         <v>0.10929987296124369</v>
@@ -398,7 +398,7 @@
         <v>-0.092838053094160655</v>
       </c>
       <c r="N2" s="0">
-        <v>-0.2817003034265031</v>
+        <v>-0.25780572265416479</v>
       </c>
       <c r="O2" s="0">
         <v>1</v>
@@ -425,7 +425,7 @@
         <v>3</v>
       </c>
       <c r="W2" s="0">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="X2" s="0">
         <v>100</v>
@@ -437,10 +437,10 @@
         <v>95.617529880478088</v>
       </c>
       <c r="AA2" s="0">
-        <v>72.151394422310773</v>
+        <v>93.525896414342625</v>
       </c>
       <c r="AB2" s="0">
-        <v>9.3499999999999979</v>
+        <v>5</v>
       </c>
       <c r="AC2" s="0">
         <v>0</v>
@@ -449,7 +449,7 @@
         <v>-4.3780205591552495</v>
       </c>
       <c r="AE2" s="0">
-        <v>-5.2731567886524555</v>
+        <v>-7.462995173638598</v>
       </c>
       <c r="AF2" s="0">
         <v>0</v>
@@ -458,7 +458,7 @@
         <v>3.3306690738754696e-14</v>
       </c>
       <c r="AH2" s="0">
-        <v>4.8160742970537518</v>
+        <v>-0.22457596375445865</v>
       </c>
       <c r="AI2" s="0">
         <v>0</v>
@@ -467,7 +467,7 @@
         <v>-0.20213792605540434</v>
       </c>
       <c r="AK2" s="0">
-        <v>-0.39100017638774676</v>
+        <v>-0.36710559561540845</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>34.231854886127543</v>
       </c>
       <c r="H3" s="0">
-        <v>25.080247347154373</v>
+        <v>34.480142582456793</v>
       </c>
       <c r="I3" s="0">
         <v>-10.977189830693035</v>
@@ -502,7 +502,7 @@
         <v>-10.977189830693002</v>
       </c>
       <c r="K3" s="0">
-        <v>-8.0217714720302151</v>
+        <v>-10.977189830693002</v>
       </c>
       <c r="L3" s="0">
         <v>2.1156923103317657</v>
@@ -511,7 +511,7 @@
         <v>2.013074174394379</v>
       </c>
       <c r="N3" s="0">
-        <v>2.0237723658766131</v>
+        <v>2.0272617455506738</v>
       </c>
       <c r="O3" s="0">
         <v>1</v>
@@ -538,7 +538,7 @@
         <v>1</v>
       </c>
       <c r="W3" s="0">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="X3" s="0">
         <v>100</v>
@@ -550,10 +550,10 @@
         <v>98.412698412698404</v>
       </c>
       <c r="AA3" s="0">
-        <v>78.472222222222229</v>
+        <v>98.313492063492063</v>
       </c>
       <c r="AB3" s="0">
-        <v>6.3499999999999996</v>
+        <v>1.5</v>
       </c>
       <c r="AC3" s="0">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>-4.7271132707838115</v>
       </c>
       <c r="AE3" s="0">
-        <v>-13.878720809756985</v>
+        <v>-4.4788255744545591</v>
       </c>
       <c r="AF3" s="0">
         <v>0</v>
@@ -571,7 +571,7 @@
         <v>3.3306690738754696e-14</v>
       </c>
       <c r="AH3" s="0">
-        <v>2.9554183586628202</v>
+        <v>3.3306690738754696e-14</v>
       </c>
       <c r="AI3" s="0">
         <v>0</v>
@@ -580,7 +580,7 @@
         <v>-0.10261813593738678</v>
       </c>
       <c r="AK3" s="0">
-        <v>-0.091919944455152613</v>
+        <v>-0.088430564781091903</v>
       </c>
     </row>
     <row r="4">
@@ -606,7 +606,7 @@
         <v>61.523048897890334</v>
       </c>
       <c r="H4" s="0">
-        <v>46.869142634234251</v>
+        <v>57.423709980608486</v>
       </c>
       <c r="I4" s="0">
         <v>-28.555538592397166</v>
@@ -615,7 +615,7 @@
         <v>-14.690460020751194</v>
       </c>
       <c r="K4" s="0">
-        <v>-12.072524537803741</v>
+        <v>-15.430988608304453</v>
       </c>
       <c r="L4" s="0">
         <v>1.2881262992720548</v>
@@ -624,7 +624,7 @@
         <v>2.0191604728746921</v>
       </c>
       <c r="N4" s="0">
-        <v>1.9784009080502873</v>
+        <v>2.0052856167324848</v>
       </c>
       <c r="O4" s="0">
         <v>1</v>
@@ -651,7 +651,7 @@
         <v>4</v>
       </c>
       <c r="W4" s="0">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="X4" s="0">
         <v>100</v>
@@ -663,10 +663,10 @@
         <v>88.537549407114625</v>
       </c>
       <c r="AA4" s="0">
-        <v>72.529644268774746</v>
+        <v>86.758893280632407</v>
       </c>
       <c r="AB4" s="0">
-        <v>8.8999999999999986</v>
+        <v>5</v>
       </c>
       <c r="AC4" s="0">
         <v>0</v>
@@ -675,7 +675,7 @@
         <v>12.876437109045003</v>
       </c>
       <c r="AE4" s="0">
-        <v>-1.7774691546110777</v>
+        <v>8.7770981917631552</v>
       </c>
       <c r="AF4" s="0">
         <v>0</v>
@@ -684,7 +684,7 @@
         <v>13.865078571645972</v>
       </c>
       <c r="AH4" s="0">
-        <v>16.483014054593426</v>
+        <v>13.124549984092715</v>
       </c>
       <c r="AI4" s="0">
         <v>0</v>
@@ -693,7 +693,7 @@
         <v>0.73103417360263734</v>
       </c>
       <c r="AK4" s="0">
-        <v>0.69027460877823255</v>
+        <v>0.71715931746043005</v>
       </c>
     </row>
     <row r="5">
@@ -719,7 +719,7 @@
         <v>25.793981127611442</v>
       </c>
       <c r="H5" s="0">
-        <v>20.102944661229948</v>
+        <v>27.356203550900737</v>
       </c>
       <c r="I5" s="0">
         <v>-10.851164422211756</v>
@@ -728,7 +728,7 @@
         <v>-9.6136893959036023</v>
       </c>
       <c r="K5" s="0">
-        <v>-5.7471559636525722</v>
+        <v>-7.8524793546466025</v>
       </c>
       <c r="L5" s="0">
         <v>1.4213058130654794</v>
@@ -737,7 +737,7 @@
         <v>1.4304937806722802</v>
       </c>
       <c r="N5" s="0">
-        <v>1.5243718972438316</v>
+        <v>1.5230432043999615</v>
       </c>
       <c r="O5" s="0">
         <v>1</v>
@@ -764,7 +764,7 @@
         <v>2</v>
       </c>
       <c r="W5" s="0">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="X5" s="0">
         <v>100</v>
@@ -776,10 +776,10 @@
         <v>96.428571428571431</v>
       </c>
       <c r="AA5" s="0">
-        <v>75.813492063492092</v>
+        <v>95.833333333333343</v>
       </c>
       <c r="AB5" s="0">
-        <v>8.5999999999999979</v>
+        <v>2</v>
       </c>
       <c r="AC5" s="0">
         <v>0</v>
@@ -788,7 +788,7 @@
         <v>-1.6216279264246847</v>
       </c>
       <c r="AE5" s="0">
-        <v>-7.3126643928061785</v>
+        <v>-0.05940550313539017</v>
       </c>
       <c r="AF5" s="0">
         <v>0</v>
@@ -797,7 +797,7 @@
         <v>1.2374750263081546</v>
       </c>
       <c r="AH5" s="0">
-        <v>5.1040084585591838</v>
+        <v>2.9986850675651544</v>
       </c>
       <c r="AI5" s="0">
         <v>0</v>
@@ -806,7 +806,7 @@
         <v>0.0091879676068007399</v>
       </c>
       <c r="AK5" s="0">
-        <v>0.10306608417835217</v>
+        <v>0.10173739133448212</v>
       </c>
     </row>
     <row r="6">
@@ -832,7 +832,7 @@
         <v>-25.132235220401721</v>
       </c>
       <c r="H6" s="0">
-        <v>-21.068242072273225</v>
+        <v>-25.674859372894666</v>
       </c>
       <c r="I6" s="0">
         <v>-34.82849805487043</v>
@@ -841,7 +841,7 @@
         <v>-28.939803276333176</v>
       </c>
       <c r="K6" s="0">
-        <v>-22.614296836887803</v>
+        <v>-27.471911780128298</v>
       </c>
       <c r="L6" s="0">
         <v>-1.0697619943744303</v>
@@ -850,7 +850,7 @@
         <v>-1.0451428517986023</v>
       </c>
       <c r="N6" s="0">
-        <v>-1.2361883195974954</v>
+        <v>-1.1346584755090456</v>
       </c>
       <c r="O6" s="0">
         <v>1</v>
@@ -877,7 +877,7 @@
         <v>9</v>
       </c>
       <c r="W6" s="0">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="X6" s="0">
         <v>100</v>
@@ -889,10 +889,10 @@
         <v>66.533864541832671</v>
       </c>
       <c r="AA6" s="0">
-        <v>49.302788844621517</v>
+        <v>63.34661354581673</v>
       </c>
       <c r="AB6" s="0">
-        <v>12.750000000000002</v>
+        <v>10</v>
       </c>
       <c r="AC6" s="0">
         <v>0</v>
@@ -901,7 +901,7 @@
         <v>7.4445550551832662</v>
       </c>
       <c r="AE6" s="0">
-        <v>11.508548203311763</v>
+        <v>6.9019309026903226</v>
       </c>
       <c r="AF6" s="0">
         <v>0</v>
@@ -910,7 +910,7 @@
         <v>5.8886947785372517</v>
       </c>
       <c r="AH6" s="0">
-        <v>12.214201217982623</v>
+        <v>7.3565862747421278</v>
       </c>
       <c r="AI6" s="0">
         <v>0</v>
@@ -919,7 +919,7 @@
         <v>0.024619142575827979</v>
       </c>
       <c r="AK6" s="0">
-        <v>-0.16642632522306511</v>
+        <v>-0.064896481134615325</v>
       </c>
     </row>
     <row r="7">
@@ -945,7 +945,7 @@
         <v>47.54353765718524</v>
       </c>
       <c r="H7" s="0">
-        <v>36.452022486729696</v>
+        <v>45.709212404426403</v>
       </c>
       <c r="I7" s="0">
         <v>-10.77979427373389</v>
@@ -954,7 +954,7 @@
         <v>-10.779794273733811</v>
       </c>
       <c r="K7" s="0">
-        <v>-8.0085817584338308</v>
+        <v>-11.138356255321025</v>
       </c>
       <c r="L7" s="0">
         <v>2.5553125137272699</v>
@@ -963,7 +963,7 @@
         <v>2.3315810896769724</v>
       </c>
       <c r="N7" s="0">
-        <v>2.2675660552610277</v>
+        <v>2.268379333956998</v>
       </c>
       <c r="O7" s="0">
         <v>1</v>
@@ -990,7 +990,7 @@
         <v>1</v>
       </c>
       <c r="W7" s="0">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="X7" s="0">
         <v>100</v>
@@ -1002,10 +1002,10 @@
         <v>97.200000000000003</v>
       </c>
       <c r="AA7" s="0">
-        <v>77.40000000000002</v>
+        <v>96</v>
       </c>
       <c r="AB7" s="0">
-        <v>8.3499999999999996</v>
+        <v>3.5</v>
       </c>
       <c r="AC7" s="0">
         <v>0</v>
@@ -1014,7 +1014,7 @@
         <v>-7.2309229100616434</v>
       </c>
       <c r="AE7" s="0">
-        <v>-18.322438080517188</v>
+        <v>-9.0652481628204828</v>
       </c>
       <c r="AF7" s="0">
         <v>0</v>
@@ -1023,7 +1023,7 @@
         <v>7.7715611723760958e-14</v>
       </c>
       <c r="AH7" s="0">
-        <v>2.7712125153000589</v>
+        <v>-0.35856198158713548</v>
       </c>
       <c r="AI7" s="0">
         <v>0</v>
@@ -1032,7 +1032,7 @@
         <v>-0.22373142405029744</v>
       </c>
       <c r="AK7" s="0">
-        <v>-0.28774645846624214</v>
+        <v>-0.28693317977027188</v>
       </c>
     </row>
     <row r="8">
@@ -1058,7 +1058,7 @@
         <v>19.143199015732982</v>
       </c>
       <c r="H8" s="0">
-        <v>11.823825591436755</v>
+        <v>18.276307712844453</v>
       </c>
       <c r="I8" s="0">
         <v>-13.557819053325337</v>
@@ -1067,7 +1067,7 @@
         <v>-15.361647384867293</v>
       </c>
       <c r="K8" s="0">
-        <v>-10.750324194239314</v>
+        <v>-14.836996851409767</v>
       </c>
       <c r="L8" s="0">
         <v>1.3552713153828093</v>
@@ -1076,7 +1076,7 @@
         <v>1.1482499157946466</v>
       </c>
       <c r="N8" s="0">
-        <v>0.9634445426631002</v>
+        <v>1.1140076211675034</v>
       </c>
       <c r="O8" s="0">
         <v>1</v>
@@ -1103,7 +1103,7 @@
         <v>2</v>
       </c>
       <c r="W8" s="0">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="X8" s="0">
         <v>100</v>
@@ -1115,10 +1115,10 @@
         <v>94.444444444444443</v>
       </c>
       <c r="AA8" s="0">
-        <v>73.888888888888886</v>
+        <v>93.452380952380949</v>
       </c>
       <c r="AB8" s="0">
-        <v>9.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="AC8" s="0">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>-6.4349753775560625</v>
       </c>
       <c r="AE8" s="0">
-        <v>-13.75434880185229</v>
+        <v>-7.3018666804445909</v>
       </c>
       <c r="AF8" s="0">
         <v>0</v>
@@ -1136,7 +1136,7 @@
         <v>-1.8038283315419568</v>
       </c>
       <c r="AH8" s="0">
-        <v>2.8074948590860238</v>
+        <v>-1.2791777980844299</v>
       </c>
       <c r="AI8" s="0">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         <v>-0.20702139958816268</v>
       </c>
       <c r="AK8" s="0">
-        <v>-0.39182677271970912</v>
+        <v>-0.24126369421530591</v>
       </c>
     </row>
     <row r="9">
@@ -1171,7 +1171,7 @@
         <v>14.880317265055321</v>
       </c>
       <c r="H9" s="0">
-        <v>9.2212972248572953</v>
+        <v>17.136217568679779</v>
       </c>
       <c r="I9" s="0">
         <v>-22.768355184633116</v>
@@ -1180,7 +1180,7 @@
         <v>-26.273655940866458</v>
       </c>
       <c r="K9" s="0">
-        <v>-18.983435327603026</v>
+        <v>-24.772856997802283</v>
       </c>
       <c r="L9" s="0">
         <v>0.90766215046721255</v>
@@ -1189,7 +1189,7 @@
         <v>0.71767420956184058</v>
       </c>
       <c r="N9" s="0">
-        <v>0.64191734380263643</v>
+        <v>0.81888490001355829</v>
       </c>
       <c r="O9" s="0">
         <v>1</v>
@@ -1216,7 +1216,7 @@
         <v>2</v>
       </c>
       <c r="W9" s="0">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="X9" s="0">
         <v>100</v>
@@ -1228,10 +1228,10 @@
         <v>95.599999999999994</v>
       </c>
       <c r="AA9" s="0">
-        <v>75.100000000000009</v>
+        <v>94.699999999999989</v>
       </c>
       <c r="AB9" s="0">
-        <v>7.8999999999999986</v>
+        <v>3</v>
       </c>
       <c r="AC9" s="0">
         <v>0</v>
@@ -1240,7 +1240,7 @@
         <v>-5.4619562128638721</v>
       </c>
       <c r="AE9" s="0">
-        <v>-11.120976253061897</v>
+        <v>-3.2060559092394136</v>
       </c>
       <c r="AF9" s="0">
         <v>0</v>
@@ -1249,7 +1249,7 @@
         <v>-3.5053007562333427</v>
       </c>
       <c r="AH9" s="0">
-        <v>3.784919857030089</v>
+        <v>-2.0045018131691683</v>
       </c>
       <c r="AI9" s="0">
         <v>0</v>
@@ -1258,7 +1258,7 @@
         <v>-0.18998794090537197</v>
       </c>
       <c r="AK9" s="0">
-        <v>-0.26574480666457612</v>
+        <v>-0.088777250453654255</v>
       </c>
     </row>
     <row r="10">
@@ -1284,7 +1284,7 @@
         <v>20.185248490175912</v>
       </c>
       <c r="H10" s="0">
-        <v>16.393629153729684</v>
+        <v>20.185248490175912</v>
       </c>
       <c r="I10" s="0">
         <v>-11.83474937620419</v>
@@ -1293,7 +1293,7 @@
         <v>-11.83474937620419</v>
       </c>
       <c r="K10" s="0">
-        <v>-8.5873381591971771</v>
+        <v>-11.83474937620419</v>
       </c>
       <c r="L10" s="0">
         <v>2.6103479861647885</v>
@@ -1302,7 +1302,7 @@
         <v>2.6103479861647885</v>
       </c>
       <c r="N10" s="0">
-        <v>2.7306819884636302</v>
+        <v>2.6103479861647885</v>
       </c>
       <c r="O10" s="0">
         <v>1</v>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="W10" s="0">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="X10" s="0">
         <v>100</v>
@@ -1341,10 +1341,10 @@
         <v>100</v>
       </c>
       <c r="AA10" s="0">
-        <v>79.215686274509807</v>
+        <v>100</v>
       </c>
       <c r="AB10" s="0">
-        <v>2.6999999999999997</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="0">
         <v>0</v>
@@ -1353,7 +1353,7 @@
         <v>0</v>
       </c>
       <c r="AE10" s="0">
-        <v>-3.7916193364462281</v>
+        <v>0</v>
       </c>
       <c r="AF10" s="0">
         <v>0</v>
@@ -1362,7 +1362,7 @@
         <v>0</v>
       </c>
       <c r="AH10" s="0">
-        <v>3.2474112170070124</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="0">
         <v>0</v>
@@ -1371,7 +1371,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="0">
-        <v>0.12033400229884172</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/results/walkforward/walk_forward_QQQ.xlsx
+++ b/results/walkforward/walk_forward_QQQ.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="192" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="376" uniqueCount="48">
   <si>
     <t>Ticker</t>
   </si>
@@ -377,28 +377,28 @@
         <v>-0.11405355793117078</v>
       </c>
       <c r="G2" s="0">
-        <v>-4.4920741170864193</v>
+        <v>-4.0975711656975555</v>
       </c>
       <c r="H2" s="0">
-        <v>-7.5770487315697688</v>
+        <v>-8.616463078543724</v>
       </c>
       <c r="I2" s="0">
         <v>-22.799679280511707</v>
       </c>
       <c r="J2" s="0">
-        <v>-22.799679280511675</v>
+        <v>-22.799679280511796</v>
       </c>
       <c r="K2" s="0">
-        <v>-23.024255244266168</v>
+        <v>-22.387230703694073</v>
       </c>
       <c r="L2" s="0">
         <v>0.10929987296124369</v>
       </c>
       <c r="M2" s="0">
-        <v>-0.092838053094160655</v>
+        <v>-0.074846046557122278</v>
       </c>
       <c r="N2" s="0">
-        <v>-0.25780572265416479</v>
+        <v>-0.30895122434474043</v>
       </c>
       <c r="O2" s="0">
         <v>1</v>
@@ -413,61 +413,61 @@
         <v>0</v>
       </c>
       <c r="S2" s="0">
+        <v>1</v>
+      </c>
+      <c r="T2" s="0">
+        <v>1</v>
+      </c>
+      <c r="U2" s="0">
+        <v>0</v>
+      </c>
+      <c r="V2" s="0">
         <v>2</v>
       </c>
-      <c r="T2" s="0">
-        <v>2</v>
-      </c>
-      <c r="U2" s="0">
-        <v>0</v>
-      </c>
-      <c r="V2" s="0">
-        <v>3</v>
-      </c>
       <c r="W2" s="0">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="X2" s="0">
         <v>100</v>
       </c>
       <c r="Y2" s="0">
-        <v>95.617529880478088</v>
+        <v>96.414342629482078</v>
       </c>
       <c r="Z2" s="0">
-        <v>95.617529880478088</v>
+        <v>96.414342629482078</v>
       </c>
       <c r="AA2" s="0">
-        <v>93.525896414342625</v>
+        <v>93.924302788844628</v>
       </c>
       <c r="AB2" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC2" s="0">
         <v>0</v>
       </c>
       <c r="AD2" s="0">
-        <v>-4.3780205591552495</v>
+        <v>-3.9835176077663847</v>
       </c>
       <c r="AE2" s="0">
-        <v>-7.462995173638598</v>
+        <v>-8.5024095206125523</v>
       </c>
       <c r="AF2" s="0">
         <v>0</v>
       </c>
       <c r="AG2" s="0">
-        <v>3.3306690738754696e-14</v>
+        <v>-8.8817841970012523e-14</v>
       </c>
       <c r="AH2" s="0">
-        <v>-0.22457596375445865</v>
+        <v>0.41244857681763669</v>
       </c>
       <c r="AI2" s="0">
         <v>0</v>
       </c>
       <c r="AJ2" s="0">
-        <v>-0.20213792605540434</v>
+        <v>-0.18414591951836595</v>
       </c>
       <c r="AK2" s="0">
-        <v>-0.36710559561540845</v>
+        <v>-0.41825109730598409</v>
       </c>
     </row>
     <row r="3">
@@ -490,37 +490,37 @@
         <v>38.958968156911354</v>
       </c>
       <c r="G3" s="0">
-        <v>34.231854886127543</v>
+        <v>38.958968156911354</v>
       </c>
       <c r="H3" s="0">
-        <v>34.480142582456793</v>
+        <v>40.951972442727282</v>
       </c>
       <c r="I3" s="0">
         <v>-10.977189830693035</v>
       </c>
       <c r="J3" s="0">
-        <v>-10.977189830693002</v>
+        <v>-10.977189830693035</v>
       </c>
       <c r="K3" s="0">
-        <v>-10.977189830693002</v>
+        <v>-10.977189830693025</v>
       </c>
       <c r="L3" s="0">
         <v>2.1156923103317657</v>
       </c>
       <c r="M3" s="0">
-        <v>2.013074174394379</v>
+        <v>2.1156923103317657</v>
       </c>
       <c r="N3" s="0">
-        <v>2.0272617455506738</v>
+        <v>2.237211101752862</v>
       </c>
       <c r="O3" s="0">
         <v>1</v>
       </c>
       <c r="P3" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" s="0">
         <v>0</v>
@@ -535,52 +535,52 @@
         <v>0</v>
       </c>
       <c r="V3" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X3" s="0">
         <v>100</v>
       </c>
       <c r="Y3" s="0">
-        <v>98.412698412698404</v>
+        <v>100</v>
       </c>
       <c r="Z3" s="0">
-        <v>98.412698412698404</v>
+        <v>100</v>
       </c>
       <c r="AA3" s="0">
-        <v>98.313492063492063</v>
+        <v>99.801587301587304</v>
       </c>
       <c r="AB3" s="0">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="AC3" s="0">
         <v>0</v>
       </c>
       <c r="AD3" s="0">
-        <v>-4.7271132707838115</v>
+        <v>0</v>
       </c>
       <c r="AE3" s="0">
-        <v>-4.4788255744545591</v>
+        <v>1.9930042858159247</v>
       </c>
       <c r="AF3" s="0">
         <v>0</v>
       </c>
       <c r="AG3" s="0">
-        <v>3.3306690738754696e-14</v>
+        <v>0</v>
       </c>
       <c r="AH3" s="0">
-        <v>3.3306690738754696e-14</v>
+        <v>1.1102230246251565e-14</v>
       </c>
       <c r="AI3" s="0">
         <v>0</v>
       </c>
       <c r="AJ3" s="0">
-        <v>-0.10261813593738678</v>
+        <v>0</v>
       </c>
       <c r="AK3" s="0">
-        <v>-0.088430564781091903</v>
+        <v>0.12151879142109623</v>
       </c>
     </row>
     <row r="4">
@@ -603,28 +603,28 @@
         <v>48.646611788845327</v>
       </c>
       <c r="G4" s="0">
-        <v>61.523048897890334</v>
+        <v>60.956505913153961</v>
       </c>
       <c r="H4" s="0">
-        <v>57.423709980608486</v>
+        <v>63.021205158685881</v>
       </c>
       <c r="I4" s="0">
         <v>-28.555538592397166</v>
       </c>
       <c r="J4" s="0">
-        <v>-14.690460020751194</v>
+        <v>-15.080854712824621</v>
       </c>
       <c r="K4" s="0">
-        <v>-15.430988608304453</v>
+        <v>-14.011437266697868</v>
       </c>
       <c r="L4" s="0">
         <v>1.2881262992720548</v>
       </c>
       <c r="M4" s="0">
-        <v>2.0191604728746921</v>
+        <v>2.0312327785922815</v>
       </c>
       <c r="N4" s="0">
-        <v>2.0052856167324848</v>
+        <v>2.1428188232063894</v>
       </c>
       <c r="O4" s="0">
         <v>1</v>
@@ -651,49 +651,49 @@
         <v>4</v>
       </c>
       <c r="W4" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X4" s="0">
         <v>100</v>
       </c>
       <c r="Y4" s="0">
-        <v>88.537549407114625</v>
+        <v>88.932806324110672</v>
       </c>
       <c r="Z4" s="0">
-        <v>88.537549407114625</v>
+        <v>88.932806324110672</v>
       </c>
       <c r="AA4" s="0">
-        <v>86.758893280632407</v>
+        <v>87.351778656126484</v>
       </c>
       <c r="AB4" s="0">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AC4" s="0">
         <v>0</v>
       </c>
       <c r="AD4" s="0">
-        <v>12.876437109045003</v>
+        <v>12.309894124308629</v>
       </c>
       <c r="AE4" s="0">
-        <v>8.7770981917631552</v>
+        <v>14.37459336984055</v>
       </c>
       <c r="AF4" s="0">
         <v>0</v>
       </c>
       <c r="AG4" s="0">
-        <v>13.865078571645972</v>
+        <v>13.474683879572547</v>
       </c>
       <c r="AH4" s="0">
-        <v>13.124549984092715</v>
+        <v>14.544101325699298</v>
       </c>
       <c r="AI4" s="0">
         <v>0</v>
       </c>
       <c r="AJ4" s="0">
-        <v>0.73103417360263734</v>
+        <v>0.74310647932022666</v>
       </c>
       <c r="AK4" s="0">
-        <v>0.71715931746043005</v>
+        <v>0.85469252393433459</v>
       </c>
     </row>
     <row r="5">
@@ -716,97 +716,97 @@
         <v>27.415609054036128</v>
       </c>
       <c r="G5" s="0">
-        <v>25.793981127611442</v>
+        <v>27.415609054036128</v>
       </c>
       <c r="H5" s="0">
-        <v>27.356203550900737</v>
+        <v>25.778867651605687</v>
       </c>
       <c r="I5" s="0">
         <v>-10.851164422211756</v>
       </c>
       <c r="J5" s="0">
-        <v>-9.6136893959036023</v>
+        <v>-10.851164422211756</v>
       </c>
       <c r="K5" s="0">
-        <v>-7.8524793546466025</v>
+        <v>-10.874101252116141</v>
       </c>
       <c r="L5" s="0">
         <v>1.4213058130654794</v>
       </c>
       <c r="M5" s="0">
-        <v>1.4304937806722802</v>
+        <v>1.4213058130654794</v>
       </c>
       <c r="N5" s="0">
-        <v>1.5230432043999615</v>
+        <v>1.3666090801420134</v>
       </c>
       <c r="O5" s="0">
         <v>1</v>
       </c>
       <c r="P5" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" s="0">
         <v>0</v>
       </c>
       <c r="S5" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" s="0">
         <v>0</v>
       </c>
       <c r="V5" s="0">
+        <v>0</v>
+      </c>
+      <c r="W5" s="0">
         <v>2</v>
       </c>
-      <c r="W5" s="0">
-        <v>4</v>
-      </c>
       <c r="X5" s="0">
         <v>100</v>
       </c>
       <c r="Y5" s="0">
-        <v>96.428571428571431</v>
+        <v>100</v>
       </c>
       <c r="Z5" s="0">
-        <v>96.428571428571431</v>
+        <v>100</v>
       </c>
       <c r="AA5" s="0">
-        <v>95.833333333333343</v>
+        <v>99.603174603174608</v>
       </c>
       <c r="AB5" s="0">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="AC5" s="0">
         <v>0</v>
       </c>
       <c r="AD5" s="0">
-        <v>-1.6216279264246847</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="0">
-        <v>-0.05940550313539017</v>
+        <v>-1.6367414024304416</v>
       </c>
       <c r="AF5" s="0">
         <v>0</v>
       </c>
       <c r="AG5" s="0">
-        <v>1.2374750263081546</v>
+        <v>0</v>
       </c>
       <c r="AH5" s="0">
-        <v>2.9986850675651544</v>
+        <v>-0.022936829904385281</v>
       </c>
       <c r="AI5" s="0">
         <v>0</v>
       </c>
       <c r="AJ5" s="0">
-        <v>0.0091879676068007399</v>
+        <v>0</v>
       </c>
       <c r="AK5" s="0">
-        <v>0.10173739133448212</v>
+        <v>-0.054696732923465996</v>
       </c>
     </row>
     <row r="6">
@@ -829,97 +829,97 @@
         <v>-32.57679027558499</v>
       </c>
       <c r="G6" s="0">
-        <v>-25.132235220401721</v>
+        <v>-26.751064878716647</v>
       </c>
       <c r="H6" s="0">
-        <v>-25.674859372894666</v>
+        <v>-27.374321752207052</v>
       </c>
       <c r="I6" s="0">
         <v>-34.82849805487043</v>
       </c>
       <c r="J6" s="0">
-        <v>-28.939803276333176</v>
+        <v>-29.845656927395403</v>
       </c>
       <c r="K6" s="0">
-        <v>-27.471911780128298</v>
+        <v>-29.611078169891357</v>
       </c>
       <c r="L6" s="0">
         <v>-1.0697619943744303</v>
       </c>
       <c r="M6" s="0">
-        <v>-1.0451428517986023</v>
+        <v>-1.0876845923020129</v>
       </c>
       <c r="N6" s="0">
-        <v>-1.1346584755090456</v>
+        <v>-1.1743735502138146</v>
       </c>
       <c r="O6" s="0">
         <v>1</v>
       </c>
       <c r="P6" s="0">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="0">
+        <v>3</v>
+      </c>
+      <c r="R6" s="0">
+        <v>0</v>
+      </c>
+      <c r="S6" s="0">
         <v>4</v>
       </c>
-      <c r="Q6" s="0">
+      <c r="T6" s="0">
         <v>4</v>
       </c>
-      <c r="R6" s="0">
-        <v>0</v>
-      </c>
-      <c r="S6" s="0">
-        <v>5</v>
-      </c>
-      <c r="T6" s="0">
-        <v>5</v>
-      </c>
       <c r="U6" s="0">
         <v>0</v>
       </c>
       <c r="V6" s="0">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W6" s="0">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="X6" s="0">
         <v>100</v>
       </c>
       <c r="Y6" s="0">
-        <v>66.533864541832671</v>
+        <v>71.314741035856571</v>
       </c>
       <c r="Z6" s="0">
-        <v>66.533864541832671</v>
+        <v>71.314741035856571</v>
       </c>
       <c r="AA6" s="0">
-        <v>63.34661354581673</v>
+        <v>67.928286852589636</v>
       </c>
       <c r="AB6" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC6" s="0">
         <v>0</v>
       </c>
       <c r="AD6" s="0">
-        <v>7.4445550551832662</v>
+        <v>5.825725396868342</v>
       </c>
       <c r="AE6" s="0">
-        <v>6.9019309026903226</v>
+        <v>5.2024685233779344</v>
       </c>
       <c r="AF6" s="0">
         <v>0</v>
       </c>
       <c r="AG6" s="0">
-        <v>5.8886947785372517</v>
+        <v>4.9828411274750239</v>
       </c>
       <c r="AH6" s="0">
-        <v>7.3565862747421278</v>
+        <v>5.2174198849790692</v>
       </c>
       <c r="AI6" s="0">
         <v>0</v>
       </c>
       <c r="AJ6" s="0">
-        <v>0.024619142575827979</v>
+        <v>-0.017922597927582551</v>
       </c>
       <c r="AK6" s="0">
-        <v>-0.064896481134615325</v>
+        <v>-0.10461155583938431</v>
       </c>
     </row>
     <row r="7">
@@ -942,28 +942,28 @@
         <v>54.774460567246884</v>
       </c>
       <c r="G7" s="0">
-        <v>47.54353765718524</v>
+        <v>46.535693150408285</v>
       </c>
       <c r="H7" s="0">
-        <v>45.709212404426403</v>
+        <v>46.535693150408285</v>
       </c>
       <c r="I7" s="0">
         <v>-10.77979427373389</v>
       </c>
       <c r="J7" s="0">
-        <v>-10.779794273733811</v>
+        <v>-10.779794273733788</v>
       </c>
       <c r="K7" s="0">
-        <v>-11.138356255321025</v>
+        <v>-10.779794273733788</v>
       </c>
       <c r="L7" s="0">
         <v>2.5553125137272699</v>
       </c>
       <c r="M7" s="0">
-        <v>2.3315810896769724</v>
+        <v>2.2928776475801369</v>
       </c>
       <c r="N7" s="0">
-        <v>2.268379333956998</v>
+        <v>2.2928776475801369</v>
       </c>
       <c r="O7" s="0">
         <v>1</v>
@@ -990,49 +990,49 @@
         <v>1</v>
       </c>
       <c r="W7" s="0">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="X7" s="0">
         <v>100</v>
       </c>
       <c r="Y7" s="0">
-        <v>97.200000000000003</v>
+        <v>96.799999999999997</v>
       </c>
       <c r="Z7" s="0">
-        <v>97.200000000000003</v>
+        <v>96.799999999999997</v>
       </c>
       <c r="AA7" s="0">
-        <v>96</v>
+        <v>96.799999999999997</v>
       </c>
       <c r="AB7" s="0">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="AC7" s="0">
         <v>0</v>
       </c>
       <c r="AD7" s="0">
-        <v>-7.2309229100616434</v>
+        <v>-8.2387674168385985</v>
       </c>
       <c r="AE7" s="0">
-        <v>-9.0652481628204828</v>
+        <v>-8.2387674168385985</v>
       </c>
       <c r="AF7" s="0">
         <v>0</v>
       </c>
       <c r="AG7" s="0">
-        <v>7.7715611723760958e-14</v>
+        <v>9.9920072216264089e-14</v>
       </c>
       <c r="AH7" s="0">
-        <v>-0.35856198158713548</v>
+        <v>9.9920072216264089e-14</v>
       </c>
       <c r="AI7" s="0">
         <v>0</v>
       </c>
       <c r="AJ7" s="0">
-        <v>-0.22373142405029744</v>
+        <v>-0.26243486614713296</v>
       </c>
       <c r="AK7" s="0">
-        <v>-0.28693317977027188</v>
+        <v>-0.26243486614713296</v>
       </c>
     </row>
     <row r="8">
@@ -1055,97 +1055,97 @@
         <v>25.578174393289043</v>
       </c>
       <c r="G8" s="0">
-        <v>19.143199015732982</v>
+        <v>25.578174393289043</v>
       </c>
       <c r="H8" s="0">
-        <v>18.276307712844453</v>
+        <v>26.587524340441917</v>
       </c>
       <c r="I8" s="0">
         <v>-13.557819053325337</v>
       </c>
       <c r="J8" s="0">
-        <v>-15.361647384867293</v>
+        <v>-13.557819053325337</v>
       </c>
       <c r="K8" s="0">
-        <v>-14.836996851409767</v>
+        <v>-12.863029443651019</v>
       </c>
       <c r="L8" s="0">
         <v>1.3552713153828093</v>
       </c>
       <c r="M8" s="0">
-        <v>1.1482499157946466</v>
+        <v>1.3552713153828093</v>
       </c>
       <c r="N8" s="0">
-        <v>1.1140076211675034</v>
+        <v>1.4186450917554292</v>
       </c>
       <c r="O8" s="0">
         <v>1</v>
       </c>
       <c r="P8" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" s="0">
         <v>0</v>
       </c>
       <c r="S8" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" s="0">
         <v>0</v>
       </c>
       <c r="V8" s="0">
+        <v>0</v>
+      </c>
+      <c r="W8" s="0">
         <v>2</v>
       </c>
-      <c r="W8" s="0">
-        <v>7</v>
-      </c>
       <c r="X8" s="0">
         <v>100</v>
       </c>
       <c r="Y8" s="0">
-        <v>94.444444444444443</v>
+        <v>100</v>
       </c>
       <c r="Z8" s="0">
-        <v>94.444444444444443</v>
+        <v>100</v>
       </c>
       <c r="AA8" s="0">
-        <v>93.452380952380949</v>
+        <v>99.603174603174608</v>
       </c>
       <c r="AB8" s="0">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="AC8" s="0">
         <v>0</v>
       </c>
       <c r="AD8" s="0">
-        <v>-6.4349753775560625</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="0">
-        <v>-7.3018666804445909</v>
+        <v>1.0093499471528711</v>
       </c>
       <c r="AF8" s="0">
         <v>0</v>
       </c>
       <c r="AG8" s="0">
-        <v>-1.8038283315419568</v>
+        <v>0</v>
       </c>
       <c r="AH8" s="0">
-        <v>-1.2791777980844299</v>
+        <v>0.6947896096743178</v>
       </c>
       <c r="AI8" s="0">
         <v>0</v>
       </c>
       <c r="AJ8" s="0">
-        <v>-0.20702139958816268</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="0">
-        <v>-0.24126369421530591</v>
+        <v>0.063373776372619872</v>
       </c>
     </row>
     <row r="9">
@@ -1168,28 +1168,28 @@
         <v>20.342273477919193</v>
       </c>
       <c r="G9" s="0">
-        <v>14.880317265055321</v>
+        <v>17.7045001403892</v>
       </c>
       <c r="H9" s="0">
-        <v>17.136217568679779</v>
+        <v>20.590993783696064</v>
       </c>
       <c r="I9" s="0">
         <v>-22.768355184633116</v>
       </c>
       <c r="J9" s="0">
-        <v>-26.273655940866458</v>
+        <v>-24.46118986042929</v>
       </c>
       <c r="K9" s="0">
-        <v>-24.772856997802283</v>
+        <v>-22.923495731355636</v>
       </c>
       <c r="L9" s="0">
         <v>0.90766215046721255</v>
       </c>
       <c r="M9" s="0">
-        <v>0.71767420956184058</v>
+        <v>0.82567676762358833</v>
       </c>
       <c r="N9" s="0">
-        <v>0.81888490001355829</v>
+        <v>0.95004765981409001</v>
       </c>
       <c r="O9" s="0">
         <v>1</v>
@@ -1216,49 +1216,49 @@
         <v>2</v>
       </c>
       <c r="W9" s="0">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X9" s="0">
         <v>100</v>
       </c>
       <c r="Y9" s="0">
-        <v>95.599999999999994</v>
+        <v>94.799999999999997</v>
       </c>
       <c r="Z9" s="0">
-        <v>95.599999999999994</v>
+        <v>94.799999999999997</v>
       </c>
       <c r="AA9" s="0">
-        <v>94.699999999999989</v>
+        <v>93.799999999999997</v>
       </c>
       <c r="AB9" s="0">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AC9" s="0">
         <v>0</v>
       </c>
       <c r="AD9" s="0">
-        <v>-5.4619562128638721</v>
+        <v>-2.6377733375299917</v>
       </c>
       <c r="AE9" s="0">
-        <v>-3.2060559092394136</v>
+        <v>0.24872030577687276</v>
       </c>
       <c r="AF9" s="0">
         <v>0</v>
       </c>
       <c r="AG9" s="0">
-        <v>-3.5053007562333427</v>
+        <v>-1.6928346757961732</v>
       </c>
       <c r="AH9" s="0">
-        <v>-2.0045018131691683</v>
+        <v>-0.15514054672252087</v>
       </c>
       <c r="AI9" s="0">
         <v>0</v>
       </c>
       <c r="AJ9" s="0">
-        <v>-0.18998794090537197</v>
+        <v>-0.081985382843624222</v>
       </c>
       <c r="AK9" s="0">
-        <v>-0.088777250453654255</v>
+        <v>0.042385509346877459</v>
       </c>
     </row>
     <row r="10">
